--- a/outputs/out_input1_GPT(2).xlsx
+++ b/outputs/out_input1_GPT(2).xlsx
@@ -656,10 +656,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -668,7 +668,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Abnormal</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FN</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
